--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -18,13 +18,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -111,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -121,23 +122,25 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,9 +149,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -590,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -615,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -634,10 +639,8 @@
           <t>Blended cheapness (0=rich, 1=cheap)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B6" s="5" t="n">
+        <v>0.75</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -651,7 +654,7 @@
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -668,7 +671,7 @@
           <t>DCF intrinsic value / share</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -685,8 +688,8 @@
           <t>Market price</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>0.1</v>
+      <c r="B9" s="7" t="n">
+        <v>0.006</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -700,7 +703,7 @@
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -720,52 +723,67 @@
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -776,10 +794,10 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
@@ -849,8 +867,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>0.0453600025177002</v>
+      <c r="B5" s="9" t="n">
+        <v>0.05126999855041504</v>
       </c>
     </row>
     <row r="6">
@@ -859,7 +877,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="9" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -869,7 +887,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="10" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -879,7 +897,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="9" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -889,7 +907,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="9" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -899,7 +917,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -909,7 +927,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="9" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -919,7 +937,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -929,7 +947,7 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>-361141</v>
       </c>
     </row>
@@ -939,7 +957,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="13">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -950,18 +968,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="13">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="15">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1008,23 +1026,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="16">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="16">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="16">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="16">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1035,23 +1053,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="17">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="17">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="17">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="17">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="17">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1062,23 +1080,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="16">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="16">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="16">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="16">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="16">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1089,7 +1107,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="16">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1100,7 +1118,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="16">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1111,18 +1129,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="16">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="19">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1147,7 +1165,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="12" t="n">
         <v>2365172</v>
       </c>
     </row>
@@ -1157,7 +1175,7 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" s="12" t="n">
         <v>18173</v>
       </c>
     </row>
@@ -1167,7 +1185,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="16">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1178,17 +1196,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
-        <v>250530</v>
+      <c r="B35" s="20" t="n">
+        <v>22899500</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="21">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1199,17 +1217,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>0.1</v>
+      <c r="B37" s="22" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="23">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1229,158 +1247,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="25">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="25">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="25">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="25">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="25">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23">
+      <c r="A43" s="25">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="24">
+      <c r="D43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23">
+      <c r="A44" s="25">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="24">
+      <c r="D44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="24">
+      <c r="E44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23">
+      <c r="A45" s="25">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="24">
+      <c r="B45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="23">
+      <c r="A46" s="25">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="23">
+      <c r="A47" s="25">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1405,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1436,107 +1454,265 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>GXXM</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>GEX Management, Inc.</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>25053</v>
-      </c>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="29" t="n">
-        <v>1.13</v>
-      </c>
+      <c r="C5" s="30" t="n">
+        <v>137397</v>
+      </c>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DCAC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DCAC</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DVNHF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frontier Services Group Ltd</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>5287449</v>
+      </c>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="33" t="n">
+        <v>-3.022</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>0.258</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FUGI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FUEGO ENTERPRISES INC</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>26759</v>
+      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HLXW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HELIX WIND CORP</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>192200</v>
+      </c>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>6.617</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OPMZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1PM INDS INC</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>26292</v>
+      </c>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n">
+        <v>1.858</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SYVN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SYCAMORE VENTURES INC</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n">
+        <v>35.795</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TMGY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TERMINUS ENERGY INC</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="F12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TNKE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TANKE INCORPORATED</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>19945</v>
+      </c>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="30">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="30">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="30">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="34">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="30">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="30">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="30">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05126999855041504</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.006</v>
+        <v>0.0035</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.04963000297546387</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22899500</v>
+        <v>22899428.57142857</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.006</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>137397</v>
+        <v>80148</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0035</v>
+        <v>0.006</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04991999626159668</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22899428.57142857</v>
+        <v>22899500</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.0035</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>80148</v>
+        <v>137397</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04991999626159668</v>
+        <v>0.0498799991607666</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.006</v>
+        <v>0.0035</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04993000030517578</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22899500</v>
+        <v>22899428.57142857</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.006</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>137397</v>
+        <v>80148</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0035</v>
+        <v>0.006</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.04994999885559082</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22899428.57142857</v>
+        <v>22899500</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.0035</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>80148</v>
+        <v>137397</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04994999885559082</v>
+        <v>0.04933000087738037</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/GXXM_research.xlsx
+++ b/app/reports/GXXM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-31 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.006</v>
+        <v>0.0057</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04933000087738037</v>
+        <v>0.04928999900817871</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22899500</v>
+        <v>22899473.68421052</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.006</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>137397</v>
+        <v>130527</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
